--- a/MSC/Sample data1.xlsx
+++ b/MSC/Sample data1.xlsx
@@ -2,38 +2,37 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEll\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEll\Desktop\Masters\MSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7650" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7650" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
     <sheet name="ANOVA" sheetId="5" r:id="rId4"/>
-    <sheet name="Sample data" sheetId="1" r:id="rId5"/>
+    <sheet name="Species Richness" sheetId="6" r:id="rId5"/>
+    <sheet name="Sample data" sheetId="1" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.0" hidden="1">'Sample data'!$E$2:$E$60</definedName>
     <definedName name="_xlchart.1" hidden="1">'Sample data'!$I$1</definedName>
     <definedName name="_xlchart.2" hidden="1">'Sample data'!$I$2:$I$60</definedName>
-    <definedName name="_xlchart.3" hidden="1">'Sample data'!$I$1</definedName>
-    <definedName name="_xlchart.4" hidden="1">'Sample data'!$I$2:$I$60</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="43" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="150">
   <si>
     <t>Observation_ID</t>
   </si>
@@ -466,6 +465,24 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Count of Species_Name</t>
+  </si>
+  <si>
+    <t>Richness</t>
+  </si>
+  <si>
+    <t>Abundance</t>
+  </si>
+  <si>
+    <t>Sampling Site</t>
+  </si>
+  <si>
+    <t>Proportion</t>
+  </si>
+  <si>
+    <t>Shannon</t>
+  </si>
 </sst>
 </file>
 
@@ -796,7 +813,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -931,6 +948,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -976,7 +1008,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -990,6 +1022,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3670,7 +3705,97 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable33" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="29">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Count of Observation_ID" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Sum of Number_of_Individuals" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Average of Number_of_Individuals2" fld="8" subtotal="average" baseField="4" baseItem="1"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable33" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:T25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField dataField="1" showAll="0"/>
@@ -3835,8 +3960,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable32" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable32" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A11:T17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField dataField="1" showAll="0"/>
@@ -3993,98 +4118,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="29">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="20" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Count of Observation_ID" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-    <dataField name="Sum of Number_of_Individuals" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Average of Number_of_Individuals2" fld="8" subtotal="average" baseField="4" baseItem="1"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable34" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable34" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField showAll="0"/>
@@ -4217,7 +4252,165 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable36" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable35" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:T9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="29">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="19">
+        <item x="5"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Number_of_Individuals" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable36" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A14:T28" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField showAll="0"/>
@@ -4414,25 +4607,33 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable35" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:T9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:T17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="20" showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="5">
+      <items count="13">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
       <items count="19">
         <item x="5"/>
         <item x="12"/>
@@ -4456,7 +4657,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -4479,9 +4680,9 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="4"/>
+    <field x="3"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="13">
     <i>
       <x/>
     </i>
@@ -4493,6 +4694,30 @@
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
@@ -4561,7 +4786,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Number_of_Individuals" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Count of Species_Name" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5669,7 +5894,7 @@
         <v>29</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C22" si="0">B5/SUM(B$4:B$21)</f>
+        <f t="shared" ref="C5:C21" si="0">B5/SUM(B$4:B$21)</f>
         <v>0.14009661835748793</v>
       </c>
       <c r="D5">
@@ -6098,7 +6323,7 @@
         <v>4.2553191489361701E-2</v>
       </c>
       <c r="V5">
-        <f t="shared" ref="V5:AM8" si="0">C5/$T5</f>
+        <f t="shared" ref="V5:AL8" si="0">C5/$T5</f>
         <v>0</v>
       </c>
       <c r="W5">
@@ -9688,6 +9913,2879 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:X45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" t="s">
+        <v>111</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5">
+        <v>4</v>
+      </c>
+      <c r="U5" s="10" t="str">
+        <f>A5</f>
+        <v>AG01</v>
+      </c>
+      <c r="V5" s="9">
+        <f>SUM(COUNTIF(B5:S5,"&gt;0"))</f>
+        <v>4</v>
+      </c>
+      <c r="W5" s="9">
+        <f>T5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5">
+        <v>3</v>
+      </c>
+      <c r="U6" s="10" t="str">
+        <f t="shared" ref="U6:U16" si="0">A6</f>
+        <v>AG02</v>
+      </c>
+      <c r="V6" s="9">
+        <f t="shared" ref="V6:V16" si="1">SUM(COUNTIF(B6:S6,"&gt;0"))</f>
+        <v>3</v>
+      </c>
+      <c r="W6" s="9">
+        <f t="shared" ref="W6:W16" si="2">T6</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5">
+        <v>6</v>
+      </c>
+      <c r="U7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>AG03</v>
+      </c>
+      <c r="V7" s="9">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="W7" s="9">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5">
+        <v>7</v>
+      </c>
+      <c r="U8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>CF01</v>
+      </c>
+      <c r="V8" s="9">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="W8" s="9">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5">
+        <v>2</v>
+      </c>
+      <c r="T9" s="5">
+        <v>9</v>
+      </c>
+      <c r="U9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>CF02</v>
+      </c>
+      <c r="V9" s="9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="W9" s="9">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5">
+        <v>7</v>
+      </c>
+      <c r="U10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>CF03</v>
+      </c>
+      <c r="V10" s="9">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="W10" s="9">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5">
+        <v>3</v>
+      </c>
+      <c r="U11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>SE01</v>
+      </c>
+      <c r="V11" s="9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="W11" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5">
+        <v>1</v>
+      </c>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5">
+        <v>3</v>
+      </c>
+      <c r="U12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>SE02</v>
+      </c>
+      <c r="V12" s="9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="W12" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5">
+        <v>1</v>
+      </c>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5">
+        <v>3</v>
+      </c>
+      <c r="U13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>SE03</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="W13" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5">
+        <v>1</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5">
+        <v>2</v>
+      </c>
+      <c r="U14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>WL01</v>
+      </c>
+      <c r="V14" s="9">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="W14" s="9">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5">
+        <v>5</v>
+      </c>
+      <c r="U15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>WL02</v>
+      </c>
+      <c r="V15" s="9">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="W15" s="9">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>2</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5">
+        <v>1</v>
+      </c>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5">
+        <v>7</v>
+      </c>
+      <c r="U16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>WL03</v>
+      </c>
+      <c r="V16" s="9">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="W16" s="9">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>5</v>
+      </c>
+      <c r="H17" s="5">
+        <v>4</v>
+      </c>
+      <c r="I17" s="5">
+        <v>2</v>
+      </c>
+      <c r="J17" s="5">
+        <v>5</v>
+      </c>
+      <c r="K17" s="5">
+        <v>4</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3</v>
+      </c>
+      <c r="O17" s="5">
+        <v>4</v>
+      </c>
+      <c r="P17" s="5">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>4</v>
+      </c>
+      <c r="R17" s="5">
+        <v>2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>3</v>
+      </c>
+      <c r="T17" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f>A5</f>
+        <v>AG01</v>
+      </c>
+      <c r="B19">
+        <f>B5/$T5</f>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:T19" si="3">C5/$T5</f>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f t="shared" ref="A20:A33" si="4">A6</f>
+        <v>AG02</v>
+      </c>
+      <c r="B20">
+        <f t="shared" ref="B20:T20" si="5">B6/$T6</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="shared" si="4"/>
+        <v>AG03</v>
+      </c>
+      <c r="B21">
+        <f t="shared" ref="B21:T21" si="6">B7/$T7</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="6"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="6"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="shared" si="4"/>
+        <v>CF01</v>
+      </c>
+      <c r="B22">
+        <f t="shared" ref="B22:T22" si="7">B8/$T8</f>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="7"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="shared" si="4"/>
+        <v>CF02</v>
+      </c>
+      <c r="B23">
+        <f t="shared" ref="B23:T23" si="8">B9/$T9</f>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="8"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="8"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f t="shared" si="4"/>
+        <v>CF03</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ref="B24:T24" si="9">B10/$T10</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="9"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="shared" si="4"/>
+        <v>SE01</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:T25" si="10">B11/$T11</f>
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="10"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="10"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="10"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f t="shared" si="4"/>
+        <v>SE02</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ref="B26:T26" si="11">B12/$T12</f>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="11"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="11"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="11"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f t="shared" si="4"/>
+        <v>SE03</v>
+      </c>
+      <c r="B27">
+        <f t="shared" ref="B27:T27" si="12">B13/$T13</f>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="12"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="12"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="12"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f t="shared" si="4"/>
+        <v>WL01</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28:T28" si="13">B14/$T14</f>
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f t="shared" si="4"/>
+        <v>WL02</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ref="B29:T29" si="14">B15/$T15</f>
+        <v>0.2</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="14"/>
+        <v>0.2</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="14"/>
+        <v>0.2</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="14"/>
+        <v>0.2</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="14"/>
+        <v>0.2</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f t="shared" si="4"/>
+        <v>WL03</v>
+      </c>
+      <c r="B30">
+        <f t="shared" ref="B30:T30" si="15">B16/$T16</f>
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="15"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <f t="shared" ref="B31:T31" si="16">B17/$T17</f>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="16"/>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="16"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="16"/>
+        <v>8.4745762711864403E-2</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="16"/>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="16"/>
+        <v>8.4745762711864403E-2</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="16"/>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="16"/>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="16"/>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="16"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="16"/>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="16"/>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f>A19</f>
+        <v>AG01</v>
+      </c>
+      <c r="B33">
+        <f>SUM(IF(B19=0,0,B19*LN(B19)))</f>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:T33" si="17">SUM(IF(C19=0,0,C19*LN(C19)))</f>
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="17"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="17"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="17"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="17"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="U33">
+        <f>-SUM(B33:S33)</f>
+        <v>1.3862943611198906</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f t="shared" ref="A34:A67" si="18">A20</f>
+        <v>AG02</v>
+      </c>
+      <c r="B34">
+        <f t="shared" ref="B34:S34" si="19">SUM(IF(B20=0,0,B20*LN(B20)))</f>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="19"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="19"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <f t="shared" ref="U34:U45" si="20">-SUM(B34:S34)</f>
+        <v>1.0986122886681096</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f t="shared" si="18"/>
+        <v>AG03</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ref="B35:S35" si="21">SUM(IF(B21=0,0,B21*LN(B21)))</f>
+        <v>-0.29862657820467581</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="21"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="21"/>
+        <v>-0.29862657820467581</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="21"/>
+        <v>-0.29862657820467581</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="21"/>
+        <v>-0.29862657820467581</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="20"/>
+        <v>1.5607104090414063</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f t="shared" si="18"/>
+        <v>CF01</v>
+      </c>
+      <c r="B36">
+        <f t="shared" ref="B36:S36" si="22">SUM(IF(B22=0,0,B22*LN(B22)))</f>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="22"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="22"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="22"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="22"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="22"/>
+        <v>-0.35793227671296229</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="22"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="20"/>
+        <v>1.7478680974667573</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f t="shared" si="18"/>
+        <v>CF02</v>
+      </c>
+      <c r="B37">
+        <f t="shared" ref="B37:S37" si="23">SUM(IF(B23=0,0,B23*LN(B23)))</f>
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="23"/>
+        <v>-0.33423942150583869</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="23"/>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="23"/>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="23"/>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="23"/>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="23"/>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="23"/>
+        <v>-0.33423942150583869</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="20"/>
+        <v>1.8891591637540217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f t="shared" si="18"/>
+        <v>CF03</v>
+      </c>
+      <c r="B38">
+        <f t="shared" ref="B38:S38" si="24">SUM(IF(B24=0,0,B24*LN(B24)))</f>
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="24"/>
+        <v>-0.36312765445165868</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="24"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="24"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="24"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="24"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="20"/>
+        <v>1.4750763110546947</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f t="shared" si="18"/>
+        <v>SE01</v>
+      </c>
+      <c r="B39">
+        <f t="shared" ref="B39:S39" si="25">SUM(IF(B25=0,0,B25*LN(B25)))</f>
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="25"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="25"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="25"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="20"/>
+        <v>1.0986122886681096</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f t="shared" si="18"/>
+        <v>SE02</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ref="B40:S40" si="26">SUM(IF(B26=0,0,B26*LN(B26)))</f>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="26"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="26"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="26"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="20"/>
+        <v>1.0986122886681096</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f t="shared" si="18"/>
+        <v>SE03</v>
+      </c>
+      <c r="B41">
+        <f t="shared" ref="B41:S41" si="27">SUM(IF(B27=0,0,B27*LN(B27)))</f>
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="27"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="27"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="27"/>
+        <v>-0.36620409622270322</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="20"/>
+        <v>1.0986122886681096</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f t="shared" si="18"/>
+        <v>WL01</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ref="B42:S42" si="28">SUM(IF(B28=0,0,B28*LN(B28)))</f>
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="28"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="28"/>
+        <v>-0.34657359027997264</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="20"/>
+        <v>0.69314718055994529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f t="shared" si="18"/>
+        <v>WL02</v>
+      </c>
+      <c r="B43">
+        <f t="shared" ref="B43:S43" si="29">SUM(IF(B29=0,0,B29*LN(B29)))</f>
+        <v>-0.32188758248682009</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="29"/>
+        <v>-0.32188758248682009</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="29"/>
+        <v>-0.32188758248682009</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="29"/>
+        <v>-0.32188758248682009</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="29"/>
+        <v>-0.32188758248682009</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="20"/>
+        <v>1.6094379124341005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f t="shared" si="18"/>
+        <v>WL03</v>
+      </c>
+      <c r="B44">
+        <f t="shared" ref="B44:S44" si="30">SUM(IF(B30=0,0,B30*LN(B30)))</f>
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="30"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="30"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="30"/>
+        <v>-0.35793227671296229</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="30"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="30"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="30"/>
+        <v>-0.27798716415075903</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="20"/>
+        <v>1.7478680974667573</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="B45">
+        <f t="shared" ref="B45:S45" si="31">SUM(IF(B31=0,0,B31*LN(B31)))</f>
+        <v>-0.1514707706053022</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="31"/>
+        <v>-0.11472509367273812</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="31"/>
+        <v>-6.9110804133995243E-2</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="31"/>
+        <v>-0.20916097724335755</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="31"/>
+        <v>-0.11472509367273812</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="31"/>
+        <v>-0.20916097724335755</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="31"/>
+        <v>-0.1514707706053022</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="31"/>
+        <v>-0.11472509367273812</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="31"/>
+        <v>-0.1514707706053022</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="31"/>
+        <v>-0.18245715815497146</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="31"/>
+        <v>-0.11472509367273812</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="31"/>
+        <v>-0.1514707706053022</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="20"/>
+        <v>2.8294163228176723</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
